--- a/r4-JoanneumResearch-PreNUDGE-AppData-sleep/StructureDefinition-at-prenudge-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-sleep/StructureDefinition-at-prenudge-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T13:56:00+00:00</t>
+    <t>2026-05-18T14:18:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-sleep/StructureDefinition-at-prenudge-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-sleep/StructureDefinition-at-prenudge-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:18:35+00:00</t>
+    <t>2026-05-27T15:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-sleep/StructureDefinition-at-prenudge-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-sleep/StructureDefinition-at-prenudge-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:35:26+00:00</t>
+    <t>2026-05-28T10:55:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
